--- a/agile_my.xlsx
+++ b/agile_my.xlsx
@@ -1,19 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Spring board\AI-powered-knowledge-engine-for-smart-support-and-ticket-resolution\ai_ticket_solution\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{916FD1D5-47A1-45C2-AEAC-B128AEEEADE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Product Backlog"/>
-    <sheet r:id="rId2" sheetId="2" name="Sprint Backlog"/>
-    <sheet r:id="rId3" sheetId="3" name="Stand Up Meeting"/>
-    <sheet r:id="rId4" sheetId="4" name="Retrospection"/>
-    <sheet r:id="rId5" sheetId="5" name="Legend"/>
+    <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint Backlog" sheetId="2" r:id="rId2"/>
+    <sheet name="Stand Up Meeting" sheetId="3" r:id="rId3"/>
+    <sheet name="Retrospection" sheetId="4" r:id="rId4"/>
+    <sheet name="Legend" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -998,8 +1004,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1010,7 +1015,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1034,13 +1039,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1052,7 +1057,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF7b2c00"/>
+      <color rgb="FF7B2C00"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1066,42 +1071,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1f4e79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe2efda"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFfff2cc"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf2f2f2"/>
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFdeeaf1"/>
+        <fgColor rgb="FFDEEAF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFfce4d6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffffff"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2e75b6"/>
+        <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -1115,16 +1120,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1137,13 +1142,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF1f4e79"/>
+        <color rgb="FF1F4E79"/>
       </left>
       <right style="thin">
-        <color rgb="FF1f4e79"/>
+        <color rgb="FF1F4E79"/>
       </right>
       <top style="thin">
-        <color rgb="FF1f4e79"/>
+        <color rgb="FF1F4E79"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -1152,76 +1157,76 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFffffff"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFffffff"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFffffff"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFffffff"/>
+        <color rgb="FFFFFFFF"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFe2efda"/>
+        <color rgb="FFE2EFDA"/>
       </left>
       <right style="thin">
-        <color rgb="FFe2efda"/>
+        <color rgb="FFE2EFDA"/>
       </right>
       <top style="thin">
-        <color rgb="FFe2efda"/>
+        <color rgb="FFE2EFDA"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFe2efda"/>
+        <color rgb="FFE2EFDA"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFfff2cc"/>
+        <color rgb="FFFFF2CC"/>
       </left>
       <right style="thin">
-        <color rgb="FFfff2cc"/>
+        <color rgb="FFFFF2CC"/>
       </right>
       <top style="thin">
-        <color rgb="FFfff2cc"/>
+        <color rgb="FFFFF2CC"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFfff2cc"/>
+        <color rgb="FFFFF2CC"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFf2f2f2"/>
+        <color rgb="FFF2F2F2"/>
       </left>
       <right style="thin">
-        <color rgb="FFf2f2f2"/>
+        <color rgb="FFF2F2F2"/>
       </right>
       <top style="thin">
-        <color rgb="FFf2f2f2"/>
+        <color rgb="FFF2F2F2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFf2f2f2"/>
+        <color rgb="FFF2F2F2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFdeeaf1"/>
+        <color rgb="FFDEEAF1"/>
       </left>
       <right style="thin">
-        <color rgb="FFdeeaf1"/>
+        <color rgb="FFDEEAF1"/>
       </right>
       <top style="thin">
-        <color rgb="FFdeeaf1"/>
+        <color rgb="FFDEEAF1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFdeeaf1"/>
+        <color rgb="FFDEEAF1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1229,137 +1234,131 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="4" applyBorder="1" fontId="7" applyFont="1" fillId="8" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="7" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="9" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="5" applyBorder="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="7" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="7" applyBorder="1" fontId="7" applyFont="1" fillId="5" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1370,10 +1369,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1411,71 +1410,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1503,7 +1502,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -1526,11 +1525,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -1539,13 +1538,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1555,7 +1554,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -1564,7 +1563,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1573,7 +1572,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -1581,10 +1580,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1649,255 +1648,255 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="25" width="5.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="26" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="27" width="24.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="27" width="38.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="27" width="42.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="27" width="38.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="27" width="42.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="26" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="5" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20" customFormat="1" s="1">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="12" t="s">
         <v>159</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="28.5" customFormat="1" s="1">
-      <c r="A2" s="20">
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="19" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="19" t="s">
         <v>288</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="26" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="28.5" customFormat="1" s="1">
-      <c r="A3" s="29">
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="26" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="28.5" customFormat="1" s="1">
-      <c r="A4" s="20">
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="H4" s="26" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="28.5" customFormat="1" s="1">
-      <c r="A5" s="29">
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="22" t="s">
         <v>301</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="22" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="26" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="58" customFormat="1" s="1">
-      <c r="A6" s="20">
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="H6" s="26" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="58" customFormat="1" s="1">
-      <c r="A7" s="29">
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="20">
         <v>6</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="22" t="s">
         <v>311</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="22" t="s">
         <v>312</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="22" t="s">
         <v>313</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="H7" s="39" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="58" customFormat="1" s="1">
-      <c r="A8" s="20">
+      <c r="H7" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="H8" s="40" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="58" customFormat="1" s="1">
-      <c r="A9" s="29">
+      <c r="H8" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="22" t="s">
         <v>320</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="22" t="s">
         <v>321</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="22" t="s">
         <v>322</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="22" t="s">
         <v>323</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="H9" s="40" t="s">
-        <v>244</v>
+      <c r="H9" s="26" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1906,2568 +1905,2406 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:P51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="26" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="26" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="26" width="36.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="26" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="26" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="26" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="26" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="25" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="25" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="25" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="25" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="25" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="25" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="25" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="25" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="2" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="7" style="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="22" customFormat="1" s="1">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="32"/>
+    </row>
+    <row r="2" spans="1:16" s="1" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="P2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A3" s="37" t="s">
+    </row>
+    <row r="3" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A4" s="30" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="32"/>
+    </row>
+    <row r="4" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="20">
         <v>4</v>
       </c>
-      <c r="I4" s="29">
-        <v>0</v>
-      </c>
-      <c r="J4" s="29">
+      <c r="I4" s="20">
+        <v>0</v>
+      </c>
+      <c r="J4" s="20">
         <v>4</v>
       </c>
-      <c r="K4" s="29">
-        <v>0</v>
-      </c>
-      <c r="L4" s="29">
-        <v>0</v>
-      </c>
-      <c r="M4" s="29">
-        <v>0</v>
-      </c>
-      <c r="N4" s="29">
-        <v>0</v>
-      </c>
-      <c r="O4" s="29">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A5" s="21" t="s">
+      <c r="K4" s="20">
+        <v>0</v>
+      </c>
+      <c r="L4" s="20">
+        <v>0</v>
+      </c>
+      <c r="M4" s="20">
+        <v>0</v>
+      </c>
+      <c r="N4" s="20">
+        <v>0</v>
+      </c>
+      <c r="O4" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="13">
         <v>2</v>
       </c>
-      <c r="I5" s="20">
-        <v>0</v>
-      </c>
-      <c r="J5" s="20">
-        <v>0</v>
-      </c>
-      <c r="K5" s="20">
+      <c r="I5" s="13">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13">
         <v>2</v>
       </c>
-      <c r="L5" s="20">
-        <v>0</v>
-      </c>
-      <c r="M5" s="20">
-        <v>0</v>
-      </c>
-      <c r="N5" s="20">
-        <v>0</v>
-      </c>
-      <c r="O5" s="20">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A6" s="30" t="s">
+      <c r="L5" s="13">
+        <v>0</v>
+      </c>
+      <c r="M5" s="13">
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
+        <v>0</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="20">
         <v>3</v>
       </c>
-      <c r="I6" s="29">
-        <v>0</v>
-      </c>
-      <c r="J6" s="29">
-        <v>0</v>
-      </c>
-      <c r="K6" s="29">
+      <c r="I6" s="20">
+        <v>0</v>
+      </c>
+      <c r="J6" s="20">
+        <v>0</v>
+      </c>
+      <c r="K6" s="20">
         <v>3</v>
       </c>
-      <c r="L6" s="29">
-        <v>0</v>
-      </c>
-      <c r="M6" s="29">
-        <v>0</v>
-      </c>
-      <c r="N6" s="29">
-        <v>0</v>
-      </c>
-      <c r="O6" s="29">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A7" s="21" t="s">
+      <c r="L6" s="20">
+        <v>0</v>
+      </c>
+      <c r="M6" s="20">
+        <v>0</v>
+      </c>
+      <c r="N6" s="20">
+        <v>0</v>
+      </c>
+      <c r="O6" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="13">
         <v>4</v>
       </c>
-      <c r="I7" s="20">
-        <v>0</v>
-      </c>
-      <c r="J7" s="20">
-        <v>0</v>
-      </c>
-      <c r="K7" s="20">
-        <v>0</v>
-      </c>
-      <c r="L7" s="20">
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
         <v>4</v>
       </c>
-      <c r="M7" s="20">
-        <v>0</v>
-      </c>
-      <c r="N7" s="20">
-        <v>0</v>
-      </c>
-      <c r="O7" s="20">
-        <v>0</v>
-      </c>
-      <c r="P7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A8" s="30" t="s">
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
+      <c r="N7" s="13">
+        <v>0</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="20">
         <v>2</v>
       </c>
-      <c r="I8" s="29">
-        <v>0</v>
-      </c>
-      <c r="J8" s="29">
-        <v>0</v>
-      </c>
-      <c r="K8" s="29">
-        <v>0</v>
-      </c>
-      <c r="L8" s="29">
-        <v>0</v>
-      </c>
-      <c r="M8" s="29">
+      <c r="I8" s="20">
+        <v>0</v>
+      </c>
+      <c r="J8" s="20">
+        <v>0</v>
+      </c>
+      <c r="K8" s="20">
+        <v>0</v>
+      </c>
+      <c r="L8" s="20">
+        <v>0</v>
+      </c>
+      <c r="M8" s="20">
         <v>2</v>
       </c>
-      <c r="N8" s="29">
-        <v>0</v>
-      </c>
-      <c r="O8" s="29">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A10" s="37" t="s">
+      <c r="N8" s="20">
+        <v>0</v>
+      </c>
+      <c r="O8" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A11" s="21" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="32"/>
+    </row>
+    <row r="11" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="13">
         <v>3</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="13">
         <v>3</v>
       </c>
-      <c r="J11" s="20">
-        <v>0</v>
-      </c>
-      <c r="K11" s="20">
-        <v>0</v>
-      </c>
-      <c r="L11" s="20">
-        <v>0</v>
-      </c>
-      <c r="M11" s="20">
-        <v>0</v>
-      </c>
-      <c r="N11" s="20">
-        <v>0</v>
-      </c>
-      <c r="O11" s="20">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A12" s="30" t="s">
+      <c r="J11" s="13">
+        <v>0</v>
+      </c>
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13">
+        <v>0</v>
+      </c>
+      <c r="N11" s="13">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="G12" s="38" t="s">
+      <c r="G12" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="20">
         <v>4</v>
       </c>
-      <c r="I12" s="29">
-        <v>0</v>
-      </c>
-      <c r="J12" s="29">
+      <c r="I12" s="20">
+        <v>0</v>
+      </c>
+      <c r="J12" s="20">
         <v>4</v>
       </c>
-      <c r="K12" s="29">
-        <v>0</v>
-      </c>
-      <c r="L12" s="29">
-        <v>0</v>
-      </c>
-      <c r="M12" s="29">
-        <v>0</v>
-      </c>
-      <c r="N12" s="29">
-        <v>0</v>
-      </c>
-      <c r="O12" s="29">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A13" s="21" t="s">
+      <c r="K12" s="20">
+        <v>0</v>
+      </c>
+      <c r="L12" s="20">
+        <v>0</v>
+      </c>
+      <c r="M12" s="20">
+        <v>0</v>
+      </c>
+      <c r="N12" s="20">
+        <v>0</v>
+      </c>
+      <c r="O12" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="13">
         <v>2</v>
       </c>
-      <c r="I13" s="20">
-        <v>0</v>
-      </c>
-      <c r="J13" s="20">
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
         <v>2</v>
       </c>
-      <c r="K13" s="20">
-        <v>0</v>
-      </c>
-      <c r="L13" s="20">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20">
-        <v>0</v>
-      </c>
-      <c r="N13" s="20">
-        <v>0</v>
-      </c>
-      <c r="O13" s="20">
-        <v>0</v>
-      </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A14" s="30" t="s">
+      <c r="K13" s="13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="20">
         <v>3</v>
       </c>
-      <c r="I14" s="29">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29">
+      <c r="I14" s="20">
+        <v>0</v>
+      </c>
+      <c r="J14" s="20">
+        <v>0</v>
+      </c>
+      <c r="K14" s="20">
         <v>3</v>
       </c>
-      <c r="L14" s="29">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29">
-        <v>0</v>
-      </c>
-      <c r="N14" s="29">
-        <v>0</v>
-      </c>
-      <c r="O14" s="29">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A16" s="37" t="s">
+      <c r="L14" s="20">
+        <v>0</v>
+      </c>
+      <c r="M14" s="20">
+        <v>0</v>
+      </c>
+      <c r="N14" s="20">
+        <v>0</v>
+      </c>
+      <c r="O14" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A17" s="21" t="s">
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="32"/>
+    </row>
+    <row r="17" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G17" s="38" t="s">
+      <c r="G17" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="13">
         <v>4</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="13">
         <v>4</v>
       </c>
-      <c r="J17" s="20">
-        <v>0</v>
-      </c>
-      <c r="K17" s="20">
-        <v>0</v>
-      </c>
-      <c r="L17" s="20">
-        <v>0</v>
-      </c>
-      <c r="M17" s="20">
-        <v>0</v>
-      </c>
-      <c r="N17" s="20">
-        <v>0</v>
-      </c>
-      <c r="O17" s="20">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A18" s="30" t="s">
+      <c r="J17" s="13">
+        <v>0</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13">
+        <v>0</v>
+      </c>
+      <c r="O17" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G18" s="38" t="s">
+      <c r="G18" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="20">
         <v>5</v>
       </c>
-      <c r="I18" s="29">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29">
+      <c r="I18" s="20">
+        <v>0</v>
+      </c>
+      <c r="J18" s="20">
         <v>5</v>
       </c>
-      <c r="K18" s="29">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29">
-        <v>0</v>
-      </c>
-      <c r="N18" s="29">
-        <v>0</v>
-      </c>
-      <c r="O18" s="29">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A19" s="21" t="s">
+      <c r="K18" s="20">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20">
+        <v>0</v>
+      </c>
+      <c r="M18" s="20">
+        <v>0</v>
+      </c>
+      <c r="N18" s="20">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="13">
         <v>4</v>
       </c>
-      <c r="I19" s="20">
-        <v>0</v>
-      </c>
-      <c r="J19" s="20">
-        <v>0</v>
-      </c>
-      <c r="K19" s="20">
+      <c r="I19" s="13">
+        <v>0</v>
+      </c>
+      <c r="J19" s="13">
+        <v>0</v>
+      </c>
+      <c r="K19" s="13">
         <v>4</v>
       </c>
-      <c r="L19" s="20">
-        <v>0</v>
-      </c>
-      <c r="M19" s="20">
-        <v>0</v>
-      </c>
-      <c r="N19" s="20">
-        <v>0</v>
-      </c>
-      <c r="O19" s="20">
-        <v>0</v>
-      </c>
-      <c r="P19" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A20" s="30" t="s">
+      <c r="L19" s="13">
+        <v>0</v>
+      </c>
+      <c r="M19" s="13">
+        <v>0</v>
+      </c>
+      <c r="N19" s="13">
+        <v>0</v>
+      </c>
+      <c r="O19" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="20">
         <v>3</v>
       </c>
-      <c r="I20" s="29">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29">
+      <c r="I20" s="20">
+        <v>0</v>
+      </c>
+      <c r="J20" s="20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="20">
+        <v>0</v>
+      </c>
+      <c r="L20" s="20">
         <v>3</v>
       </c>
-      <c r="M20" s="29">
-        <v>0</v>
-      </c>
-      <c r="N20" s="29">
-        <v>0</v>
-      </c>
-      <c r="O20" s="29">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A21" s="21" t="s">
+      <c r="M20" s="20">
+        <v>0</v>
+      </c>
+      <c r="N20" s="20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G21" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="13">
         <v>2</v>
       </c>
-      <c r="I21" s="20">
-        <v>0</v>
-      </c>
-      <c r="J21" s="20">
-        <v>0</v>
-      </c>
-      <c r="K21" s="20">
-        <v>0</v>
-      </c>
-      <c r="L21" s="20">
-        <v>0</v>
-      </c>
-      <c r="M21" s="20">
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13">
+        <v>0</v>
+      </c>
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="13">
         <v>2</v>
       </c>
-      <c r="N21" s="20">
-        <v>0</v>
-      </c>
-      <c r="O21" s="20">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A23" s="37" t="s">
+      <c r="N21" s="13">
+        <v>0</v>
+      </c>
+      <c r="O21" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A24" s="30" t="s">
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="32"/>
+    </row>
+    <row r="24" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="20">
         <v>6</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="20">
         <v>6</v>
       </c>
-      <c r="J24" s="29">
-        <v>0</v>
-      </c>
-      <c r="K24" s="29">
-        <v>0</v>
-      </c>
-      <c r="L24" s="29">
-        <v>0</v>
-      </c>
-      <c r="M24" s="29">
-        <v>0</v>
-      </c>
-      <c r="N24" s="29">
-        <v>0</v>
-      </c>
-      <c r="O24" s="29">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A25" s="21" t="s">
+      <c r="J24" s="20">
+        <v>0</v>
+      </c>
+      <c r="K24" s="20">
+        <v>0</v>
+      </c>
+      <c r="L24" s="20">
+        <v>0</v>
+      </c>
+      <c r="M24" s="20">
+        <v>0</v>
+      </c>
+      <c r="N24" s="20">
+        <v>0</v>
+      </c>
+      <c r="O24" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G25" s="38" t="s">
+      <c r="G25" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="13">
         <v>4</v>
       </c>
-      <c r="I25" s="20">
-        <v>0</v>
-      </c>
-      <c r="J25" s="20">
+      <c r="I25" s="13">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13">
         <v>4</v>
       </c>
-      <c r="K25" s="20">
-        <v>0</v>
-      </c>
-      <c r="L25" s="20">
-        <v>0</v>
-      </c>
-      <c r="M25" s="20">
-        <v>0</v>
-      </c>
-      <c r="N25" s="20">
-        <v>0</v>
-      </c>
-      <c r="O25" s="20">
-        <v>0</v>
-      </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A26" s="30" t="s">
+      <c r="K25" s="13">
+        <v>0</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="13">
+        <v>0</v>
+      </c>
+      <c r="N25" s="13">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G26" s="38" t="s">
+      <c r="G26" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="20">
         <v>3</v>
       </c>
-      <c r="I26" s="29">
-        <v>0</v>
-      </c>
-      <c r="J26" s="29">
-        <v>0</v>
-      </c>
-      <c r="K26" s="29">
+      <c r="I26" s="20">
+        <v>0</v>
+      </c>
+      <c r="J26" s="20">
+        <v>0</v>
+      </c>
+      <c r="K26" s="20">
         <v>3</v>
       </c>
-      <c r="L26" s="29">
-        <v>0</v>
-      </c>
-      <c r="M26" s="29">
-        <v>0</v>
-      </c>
-      <c r="N26" s="29">
-        <v>0</v>
-      </c>
-      <c r="O26" s="29">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A27" s="21" t="s">
+      <c r="L26" s="20">
+        <v>0</v>
+      </c>
+      <c r="M26" s="20">
+        <v>0</v>
+      </c>
+      <c r="N26" s="20">
+        <v>0</v>
+      </c>
+      <c r="O26" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="13">
         <v>2</v>
       </c>
-      <c r="I27" s="20">
-        <v>0</v>
-      </c>
-      <c r="J27" s="20">
-        <v>0</v>
-      </c>
-      <c r="K27" s="20">
-        <v>0</v>
-      </c>
-      <c r="L27" s="20">
-        <v>0</v>
-      </c>
-      <c r="M27" s="20">
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="13">
         <v>2</v>
       </c>
-      <c r="N27" s="20">
-        <v>0</v>
-      </c>
-      <c r="O27" s="20">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="36"/>
-      <c r="P28" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A29" s="37" t="s">
+      <c r="N27" s="13">
+        <v>0</v>
+      </c>
+      <c r="O27" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A30" s="30" t="s">
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="32"/>
+    </row>
+    <row r="30" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="30" t="s">
+      <c r="E30" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G30" s="38" t="s">
+      <c r="G30" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="20">
         <v>5</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="20">
         <v>5</v>
       </c>
-      <c r="J30" s="29">
-        <v>0</v>
-      </c>
-      <c r="K30" s="29">
-        <v>0</v>
-      </c>
-      <c r="L30" s="29">
-        <v>0</v>
-      </c>
-      <c r="M30" s="29">
-        <v>0</v>
-      </c>
-      <c r="N30" s="29">
-        <v>0</v>
-      </c>
-      <c r="O30" s="29">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A31" s="21" t="s">
+      <c r="J30" s="20">
+        <v>0</v>
+      </c>
+      <c r="K30" s="20">
+        <v>0</v>
+      </c>
+      <c r="L30" s="20">
+        <v>0</v>
+      </c>
+      <c r="M30" s="20">
+        <v>0</v>
+      </c>
+      <c r="N30" s="20">
+        <v>0</v>
+      </c>
+      <c r="O30" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G31" s="38" t="s">
+      <c r="G31" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="13">
         <v>4</v>
       </c>
-      <c r="I31" s="20">
-        <v>0</v>
-      </c>
-      <c r="J31" s="20">
+      <c r="I31" s="13">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13">
         <v>4</v>
       </c>
-      <c r="K31" s="20">
-        <v>0</v>
-      </c>
-      <c r="L31" s="20">
-        <v>0</v>
-      </c>
-      <c r="M31" s="20">
-        <v>0</v>
-      </c>
-      <c r="N31" s="20">
-        <v>0</v>
-      </c>
-      <c r="O31" s="20">
-        <v>0</v>
-      </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A32" s="30" t="s">
+      <c r="K31" s="13">
+        <v>0</v>
+      </c>
+      <c r="L31" s="13">
+        <v>0</v>
+      </c>
+      <c r="M31" s="13">
+        <v>0</v>
+      </c>
+      <c r="N31" s="13">
+        <v>0</v>
+      </c>
+      <c r="O31" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F32" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="G32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="20">
         <v>3</v>
       </c>
-      <c r="I32" s="29">
-        <v>0</v>
-      </c>
-      <c r="J32" s="29">
-        <v>0</v>
-      </c>
-      <c r="K32" s="29">
+      <c r="I32" s="20">
+        <v>0</v>
+      </c>
+      <c r="J32" s="20">
+        <v>0</v>
+      </c>
+      <c r="K32" s="20">
         <v>3</v>
       </c>
-      <c r="L32" s="29">
-        <v>0</v>
-      </c>
-      <c r="M32" s="29">
-        <v>0</v>
-      </c>
-      <c r="N32" s="29">
-        <v>0</v>
-      </c>
-      <c r="O32" s="29">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A33" s="21" t="s">
+      <c r="L32" s="20">
+        <v>0</v>
+      </c>
+      <c r="M32" s="20">
+        <v>0</v>
+      </c>
+      <c r="N32" s="20">
+        <v>0</v>
+      </c>
+      <c r="O32" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="G33" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="13">
         <v>3</v>
       </c>
-      <c r="I33" s="20">
-        <v>0</v>
-      </c>
-      <c r="J33" s="20">
-        <v>0</v>
-      </c>
-      <c r="K33" s="20">
-        <v>0</v>
-      </c>
-      <c r="L33" s="20">
-        <v>0</v>
-      </c>
-      <c r="M33" s="20">
-        <v>0</v>
-      </c>
-      <c r="N33" s="20">
+      <c r="I33" s="13">
+        <v>0</v>
+      </c>
+      <c r="J33" s="13">
+        <v>0</v>
+      </c>
+      <c r="K33" s="13">
+        <v>0</v>
+      </c>
+      <c r="L33" s="13">
+        <v>0</v>
+      </c>
+      <c r="M33" s="13">
+        <v>0</v>
+      </c>
+      <c r="N33" s="13">
         <v>3</v>
       </c>
-      <c r="O33" s="20">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A35" s="37" t="s">
+      <c r="O33" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
-      <c r="P35" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A36" s="30" t="s">
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="32"/>
+    </row>
+    <row r="36" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="30" t="s">
+      <c r="E36" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="F36" s="30" t="s">
+      <c r="F36" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="20">
         <v>6</v>
       </c>
-      <c r="I36" s="29">
+      <c r="I36" s="20">
         <v>6</v>
       </c>
-      <c r="J36" s="29">
-        <v>0</v>
-      </c>
-      <c r="K36" s="29">
-        <v>0</v>
-      </c>
-      <c r="L36" s="29">
-        <v>0</v>
-      </c>
-      <c r="M36" s="29">
-        <v>0</v>
-      </c>
-      <c r="N36" s="29">
-        <v>0</v>
-      </c>
-      <c r="O36" s="29">
-        <v>0</v>
-      </c>
-      <c r="P36" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A37" s="21" t="s">
+      <c r="J36" s="20">
+        <v>0</v>
+      </c>
+      <c r="K36" s="20">
+        <v>0</v>
+      </c>
+      <c r="L36" s="20">
+        <v>0</v>
+      </c>
+      <c r="M36" s="20">
+        <v>0</v>
+      </c>
+      <c r="N36" s="20">
+        <v>0</v>
+      </c>
+      <c r="O36" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="F37" s="21" t="s">
+      <c r="F37" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G37" s="39" t="s">
+      <c r="G37" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="H37" s="20">
+      <c r="H37" s="13">
         <v>5</v>
       </c>
-      <c r="I37" s="20">
-        <v>0</v>
-      </c>
-      <c r="J37" s="20">
+      <c r="I37" s="13">
+        <v>0</v>
+      </c>
+      <c r="J37" s="13">
         <v>5</v>
       </c>
-      <c r="K37" s="20">
-        <v>0</v>
-      </c>
-      <c r="L37" s="20">
-        <v>0</v>
-      </c>
-      <c r="M37" s="20">
-        <v>0</v>
-      </c>
-      <c r="N37" s="20">
-        <v>0</v>
-      </c>
-      <c r="O37" s="20">
-        <v>0</v>
-      </c>
-      <c r="P37" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A38" s="30" t="s">
+      <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="13">
+        <v>0</v>
+      </c>
+      <c r="N37" s="13">
+        <v>0</v>
+      </c>
+      <c r="O37" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="B38" s="30" t="s">
+      <c r="B38" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="D38" s="30" t="s">
+      <c r="D38" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="E38" s="30" t="s">
+      <c r="E38" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="F38" s="30" t="s">
+      <c r="F38" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G38" s="40" t="s">
+      <c r="G38" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="20">
         <v>3</v>
       </c>
-      <c r="I38" s="29">
-        <v>0</v>
-      </c>
-      <c r="J38" s="29">
-        <v>0</v>
-      </c>
-      <c r="K38" s="29">
-        <v>0</v>
-      </c>
-      <c r="L38" s="29">
+      <c r="I38" s="20">
+        <v>0</v>
+      </c>
+      <c r="J38" s="20">
+        <v>0</v>
+      </c>
+      <c r="K38" s="20">
+        <v>0</v>
+      </c>
+      <c r="L38" s="20">
         <v>3</v>
       </c>
-      <c r="M38" s="29">
-        <v>0</v>
-      </c>
-      <c r="N38" s="29">
-        <v>0</v>
-      </c>
-      <c r="O38" s="29">
-        <v>0</v>
-      </c>
-      <c r="P38" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A39" s="21" t="s">
+      <c r="M38" s="20">
+        <v>0</v>
+      </c>
+      <c r="N38" s="20">
+        <v>0</v>
+      </c>
+      <c r="O38" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="C39" s="21" t="s">
+      <c r="C39" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="F39" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G39" s="40" t="s">
+      <c r="G39" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="13">
         <v>2</v>
       </c>
-      <c r="I39" s="20">
-        <v>0</v>
-      </c>
-      <c r="J39" s="20">
-        <v>0</v>
-      </c>
-      <c r="K39" s="20">
-        <v>0</v>
-      </c>
-      <c r="L39" s="20">
-        <v>0</v>
-      </c>
-      <c r="M39" s="20">
-        <v>0</v>
-      </c>
-      <c r="N39" s="20">
+      <c r="I39" s="13">
+        <v>0</v>
+      </c>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
+      <c r="K39" s="13">
+        <v>0</v>
+      </c>
+      <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="13">
+        <v>0</v>
+      </c>
+      <c r="N39" s="13">
         <v>2</v>
       </c>
-      <c r="O39" s="20">
-        <v>0</v>
-      </c>
-      <c r="P39" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="16"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A41" s="37" t="s">
+      <c r="O39" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="36"/>
-      <c r="N41" s="36"/>
-      <c r="O41" s="36"/>
-      <c r="P41" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A42" s="30" t="s">
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="32"/>
+    </row>
+    <row r="42" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="F42" s="30" t="s">
+      <c r="F42" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G42" s="40" t="s">
+      <c r="G42" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H42" s="29">
+      <c r="H42" s="20">
         <v>5</v>
       </c>
-      <c r="I42" s="29">
-        <v>0</v>
-      </c>
-      <c r="J42" s="29">
-        <v>0</v>
-      </c>
-      <c r="K42" s="29">
-        <v>0</v>
-      </c>
-      <c r="L42" s="29">
-        <v>0</v>
-      </c>
-      <c r="M42" s="29">
-        <v>0</v>
-      </c>
-      <c r="N42" s="29">
-        <v>0</v>
-      </c>
-      <c r="O42" s="29">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A43" s="21" t="s">
+      <c r="I42" s="20">
+        <v>0</v>
+      </c>
+      <c r="J42" s="20">
+        <v>0</v>
+      </c>
+      <c r="K42" s="20">
+        <v>0</v>
+      </c>
+      <c r="L42" s="20">
+        <v>0</v>
+      </c>
+      <c r="M42" s="20">
+        <v>0</v>
+      </c>
+      <c r="N42" s="20">
+        <v>0</v>
+      </c>
+      <c r="O42" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C43" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="E43" s="21" t="s">
+      <c r="E43" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="F43" s="21" t="s">
+      <c r="F43" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G43" s="40" t="s">
+      <c r="G43" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="13">
         <v>5</v>
       </c>
-      <c r="I43" s="20">
-        <v>0</v>
-      </c>
-      <c r="J43" s="20">
-        <v>0</v>
-      </c>
-      <c r="K43" s="20">
-        <v>0</v>
-      </c>
-      <c r="L43" s="20">
-        <v>0</v>
-      </c>
-      <c r="M43" s="20">
-        <v>0</v>
-      </c>
-      <c r="N43" s="20">
-        <v>0</v>
-      </c>
-      <c r="O43" s="20">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A44" s="30" t="s">
+      <c r="I43" s="13">
+        <v>0</v>
+      </c>
+      <c r="J43" s="13">
+        <v>0</v>
+      </c>
+      <c r="K43" s="13">
+        <v>0</v>
+      </c>
+      <c r="L43" s="13">
+        <v>0</v>
+      </c>
+      <c r="M43" s="13">
+        <v>0</v>
+      </c>
+      <c r="N43" s="13">
+        <v>0</v>
+      </c>
+      <c r="O43" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="B44" s="30" t="s">
+      <c r="B44" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="D44" s="30" t="s">
+      <c r="D44" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="E44" s="30" t="s">
+      <c r="E44" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F44" s="30" t="s">
+      <c r="F44" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G44" s="40" t="s">
+      <c r="G44" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H44" s="29">
+      <c r="H44" s="20">
         <v>4</v>
       </c>
-      <c r="I44" s="29">
-        <v>0</v>
-      </c>
-      <c r="J44" s="29">
-        <v>0</v>
-      </c>
-      <c r="K44" s="29">
-        <v>0</v>
-      </c>
-      <c r="L44" s="29">
-        <v>0</v>
-      </c>
-      <c r="M44" s="29">
-        <v>0</v>
-      </c>
-      <c r="N44" s="29">
-        <v>0</v>
-      </c>
-      <c r="O44" s="29">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A45" s="21" t="s">
+      <c r="I44" s="20">
+        <v>0</v>
+      </c>
+      <c r="J44" s="20">
+        <v>0</v>
+      </c>
+      <c r="K44" s="20">
+        <v>0</v>
+      </c>
+      <c r="L44" s="20">
+        <v>0</v>
+      </c>
+      <c r="M44" s="20">
+        <v>0</v>
+      </c>
+      <c r="N44" s="20">
+        <v>0</v>
+      </c>
+      <c r="O44" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G45" s="40" t="s">
+      <c r="G45" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H45" s="20">
+      <c r="H45" s="13">
         <v>3</v>
       </c>
-      <c r="I45" s="20">
-        <v>0</v>
-      </c>
-      <c r="J45" s="20">
-        <v>0</v>
-      </c>
-      <c r="K45" s="20">
-        <v>0</v>
-      </c>
-      <c r="L45" s="20">
-        <v>0</v>
-      </c>
-      <c r="M45" s="20">
-        <v>0</v>
-      </c>
-      <c r="N45" s="20">
-        <v>0</v>
-      </c>
-      <c r="O45" s="20">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="16"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="36"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="36"/>
-      <c r="P46" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18" customFormat="1" s="1">
-      <c r="A47" s="37" t="s">
+      <c r="I45" s="13">
+        <v>0</v>
+      </c>
+      <c r="J45" s="13">
+        <v>0</v>
+      </c>
+      <c r="K45" s="13">
+        <v>0</v>
+      </c>
+      <c r="L45" s="13">
+        <v>0</v>
+      </c>
+      <c r="M45" s="13">
+        <v>0</v>
+      </c>
+      <c r="N45" s="13">
+        <v>0</v>
+      </c>
+      <c r="O45" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:16" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="36"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="36"/>
-      <c r="P47" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A48" s="30" t="s">
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="32"/>
+    </row>
+    <row r="48" spans="1:16" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C48" s="30" t="s">
+      <c r="C48" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="D48" s="30" t="s">
+      <c r="D48" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="30" t="s">
+      <c r="E48" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="F48" s="30" t="s">
+      <c r="F48" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="G48" s="40" t="s">
+      <c r="G48" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H48" s="29">
+      <c r="H48" s="20">
         <v>4</v>
       </c>
-      <c r="I48" s="29">
-        <v>0</v>
-      </c>
-      <c r="J48" s="29">
-        <v>0</v>
-      </c>
-      <c r="K48" s="29">
-        <v>0</v>
-      </c>
-      <c r="L48" s="29">
-        <v>0</v>
-      </c>
-      <c r="M48" s="29">
-        <v>0</v>
-      </c>
-      <c r="N48" s="29">
-        <v>0</v>
-      </c>
-      <c r="O48" s="29">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A49" s="21" t="s">
+      <c r="I48" s="20">
+        <v>0</v>
+      </c>
+      <c r="J48" s="20">
+        <v>0</v>
+      </c>
+      <c r="K48" s="20">
+        <v>0</v>
+      </c>
+      <c r="L48" s="20">
+        <v>0</v>
+      </c>
+      <c r="M48" s="20">
+        <v>0</v>
+      </c>
+      <c r="N48" s="20">
+        <v>0</v>
+      </c>
+      <c r="O48" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="C49" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="E49" s="21" t="s">
+      <c r="E49" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="F49" s="21" t="s">
+      <c r="F49" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G49" s="40" t="s">
+      <c r="G49" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H49" s="20">
+      <c r="H49" s="13">
         <v>6</v>
       </c>
-      <c r="I49" s="20">
-        <v>0</v>
-      </c>
-      <c r="J49" s="20">
-        <v>0</v>
-      </c>
-      <c r="K49" s="20">
-        <v>0</v>
-      </c>
-      <c r="L49" s="20">
-        <v>0</v>
-      </c>
-      <c r="M49" s="20">
-        <v>0</v>
-      </c>
-      <c r="N49" s="20">
-        <v>0</v>
-      </c>
-      <c r="O49" s="20">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A50" s="30" t="s">
+      <c r="I49" s="13">
+        <v>0</v>
+      </c>
+      <c r="J49" s="13">
+        <v>0</v>
+      </c>
+      <c r="K49" s="13">
+        <v>0</v>
+      </c>
+      <c r="L49" s="13">
+        <v>0</v>
+      </c>
+      <c r="M49" s="13">
+        <v>0</v>
+      </c>
+      <c r="N49" s="13">
+        <v>0</v>
+      </c>
+      <c r="O49" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="B50" s="30" t="s">
+      <c r="B50" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="D50" s="30" t="s">
+      <c r="D50" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="E50" s="30" t="s">
+      <c r="E50" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="F50" s="30" t="s">
+      <c r="F50" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="G50" s="40" t="s">
+      <c r="G50" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H50" s="29">
+      <c r="H50" s="20">
         <v>4</v>
       </c>
-      <c r="I50" s="29">
-        <v>0</v>
-      </c>
-      <c r="J50" s="29">
-        <v>0</v>
-      </c>
-      <c r="K50" s="29">
-        <v>0</v>
-      </c>
-      <c r="L50" s="29">
-        <v>0</v>
-      </c>
-      <c r="M50" s="29">
-        <v>0</v>
-      </c>
-      <c r="N50" s="29">
-        <v>0</v>
-      </c>
-      <c r="O50" s="29">
-        <v>0</v>
-      </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="30" customFormat="1" s="1">
-      <c r="A51" s="21" t="s">
+      <c r="I50" s="20">
+        <v>0</v>
+      </c>
+      <c r="J50" s="20">
+        <v>0</v>
+      </c>
+      <c r="K50" s="20">
+        <v>0</v>
+      </c>
+      <c r="L50" s="20">
+        <v>0</v>
+      </c>
+      <c r="M50" s="20">
+        <v>0</v>
+      </c>
+      <c r="N50" s="20">
+        <v>0</v>
+      </c>
+      <c r="O50" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D51" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="E51" s="21" t="s">
+      <c r="E51" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F51" s="21" t="s">
+      <c r="F51" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="G51" s="40" t="s">
+      <c r="G51" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="H51" s="20">
+      <c r="H51" s="13">
         <v>4</v>
       </c>
-      <c r="I51" s="20">
-        <v>0</v>
-      </c>
-      <c r="J51" s="20">
-        <v>0</v>
-      </c>
-      <c r="K51" s="20">
-        <v>0</v>
-      </c>
-      <c r="L51" s="20">
-        <v>0</v>
-      </c>
-      <c r="M51" s="20">
-        <v>0</v>
-      </c>
-      <c r="N51" s="20">
-        <v>0</v>
-      </c>
-      <c r="O51" s="20">
-        <v>0</v>
-      </c>
-      <c r="P51" s="3"/>
+      <c r="I51" s="13">
+        <v>0</v>
+      </c>
+      <c r="J51" s="13">
+        <v>0</v>
+      </c>
+      <c r="K51" s="13">
+        <v>0</v>
+      </c>
+      <c r="L51" s="13">
+        <v>0</v>
+      </c>
+      <c r="M51" s="13">
+        <v>0</v>
+      </c>
+      <c r="N51" s="13">
+        <v>0</v>
+      </c>
+      <c r="O51" s="13">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A29:P29"/>
+    <mergeCell ref="A35:P35"/>
+    <mergeCell ref="A41:P41"/>
+    <mergeCell ref="A47:P47"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="A16:P16"/>
     <mergeCell ref="A23:P23"/>
-    <mergeCell ref="A29:P29"/>
-    <mergeCell ref="A35:P35"/>
-    <mergeCell ref="A41:P41"/>
-    <mergeCell ref="A47:P47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:E37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="34" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="27" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="27" width="45.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="27" width="45.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="27" width="35.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="10" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="45" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22" customFormat="1" s="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20" customFormat="1" s="1">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A3" s="20">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A4" s="29">
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="20">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A5" s="20">
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>1</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A6" s="29">
+    <row r="6" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="20">
         <v>1</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A7" s="20">
+    <row r="7" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>1</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A8" s="29">
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20">
         <v>2</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A9" s="20">
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>2</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A10" s="29">
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="20">
         <v>2</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="22" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A11" s="20">
+    <row r="11" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A12" s="29">
+    <row r="12" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="20">
         <v>3</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A13" s="20">
+    <row r="13" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
         <v>3</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="28" t="s">
+      <c r="D13" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A14" s="29">
+    <row r="14" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20">
         <v>3</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A15" s="20">
+    <row r="15" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>3</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A16" s="29">
+    <row r="16" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="20">
         <v>3</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A17" s="20">
+    <row r="17" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
         <v>4</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A18" s="29">
+    <row r="18" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="20">
         <v>4</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A19" s="20">
+    <row r="19" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="13">
         <v>4</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A20" s="29">
+    <row r="20" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="20">
         <v>4</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A21" s="20">
+    <row r="21" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
         <v>5</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A22" s="29">
+    <row r="22" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20">
         <v>5</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A23" s="20">
+    <row r="23" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
         <v>5</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D23" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A24" s="29">
+    <row r="24" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20">
         <v>5</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A25" s="20">
+    <row r="25" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
         <v>6</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A26" s="29">
+    <row r="26" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="20">
         <v>6</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A27" s="20">
+    <row r="27" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
         <v>6</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="19" t="s">
         <v>151</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A28" s="32"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A29" s="33"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A30" s="32"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A31" s="33"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A32" s="32"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A33" s="33"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A34" s="32"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A35" s="33"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A36" s="32"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="28" customFormat="1" s="1">
-      <c r="A37" s="33"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
+    <row r="28" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="23"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="24"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+    </row>
+    <row r="30" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="23"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="24"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+    </row>
+    <row r="32" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="23"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="24"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+    </row>
+    <row r="34" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="23"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+    </row>
+    <row r="36" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="23"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="24"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4478,260 +4315,257 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="25" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="26" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="26" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="26" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="27" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="27" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="27" width="40.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="27" width="42.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="6" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="40" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22" customFormat="1" s="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20" customFormat="1" s="1">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A3" s="20">
+    <row r="3" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A4" s="20">
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A5" s="20">
+    <row r="5" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A6" s="20">
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A7" s="20">
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="13">
         <v>5</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A8" s="20">
+    <row r="8" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
         <v>6</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A9" s="20">
+    <row r="9" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
         <v>7</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="24"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="60" customFormat="1" s="1">
-      <c r="A10" s="20">
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
         <v>8</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24" t="s">
+      <c r="F10" s="17"/>
+      <c r="G10" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="24"/>
+      <c r="H10" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4742,81 +4576,77 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="13" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="14" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="50.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="6" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22" customFormat="1" s="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+    </row>
+    <row r="2" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20">
-      <c r="A3" s="7"/>
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20">
-      <c r="A4" s="8"/>
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20">
-      <c r="A5" s="9"/>
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20">
-      <c r="A6" s="10"/>
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="11"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A8" s="12" t="s">
+    <row r="7" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
